--- a/MainTop/28.08.2026 Макс Озон/print_print_sorted.xlsx
+++ b/MainTop/28.08.2026 Макс Озон/print_print_sorted.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\28.08.2026 Макс Озон\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxim\Documents\GitHub\Ozon_upload\MainTop\28.08.2026 Макс Озон\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96B989CC-83EA-4CEE-80F3-E5D619374BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9945EBA3-D75A-4173-B23A-680533799560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -655,7 +655,12 @@
   <dimension ref="A1:L68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.140625" customWidth="1"/>
+    <col min="1" max="1" width="33.85546875" customWidth="1"/>
+    <col min="2" max="8" width="4" customWidth="1"/>
+    <col min="9" max="9" width="3.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.42578125" customWidth="1"/>
+    <col min="11" max="11" width="2.5703125" customWidth="1"/>
+    <col min="12" max="12" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3244,5 +3249,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>